--- a/Results.xlsx
+++ b/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DED4465-3293-4E90-BD61-10165C7EBC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658E56BC-F181-4AF6-A949-FA68FBB40E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
   </bookViews>
@@ -90,7 +90,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,14 +126,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -136,6 +149,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>124563</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C183262F-1EA1-0A4D-0542-A695BBF4279B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4001238" y="3162300"/>
+          <a:ext cx="4437912" cy="2105024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,7 +546,13 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="D2">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0.49</v>
+      </c>
+      <c r="D2" s="1">
         <v>0.92900000000000005</v>
       </c>
       <c r="E2">
@@ -495,7 +563,13 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>5.01</v>
+      </c>
+      <c r="D3" s="1">
         <v>0.95</v>
       </c>
       <c r="E3">
@@ -506,7 +580,13 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="B4" s="1">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="C4">
+        <v>4094</v>
+      </c>
+      <c r="D4" s="1">
         <v>0.98</v>
       </c>
       <c r="E4">
@@ -517,7 +597,13 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
+      <c r="B5" s="1">
+        <v>0.82350000000000001</v>
+      </c>
+      <c r="C5">
+        <v>3.82</v>
+      </c>
+      <c r="D5" s="1">
         <v>0.95699999999999996</v>
       </c>
       <c r="E5">
@@ -528,7 +614,13 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="B6" s="1">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="C6">
+        <v>12.6</v>
+      </c>
+      <c r="D6" s="1">
         <v>0.51100000000000001</v>
       </c>
       <c r="E6">
@@ -539,7 +631,13 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="B7" s="1">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="C7">
+        <v>0.875</v>
+      </c>
+      <c r="D7" s="1">
         <v>0.79700000000000004</v>
       </c>
       <c r="E7">
@@ -550,7 +648,13 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="D8">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2.9</v>
+      </c>
+      <c r="D8" s="1">
         <v>0.66400000000000003</v>
       </c>
       <c r="E8">
@@ -561,7 +665,13 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="B9" s="1">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="C9">
+        <v>3.7</v>
+      </c>
+      <c r="D9" s="1">
         <v>0.77</v>
       </c>
       <c r="E9">
@@ -572,7 +682,13 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="D10">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>5.03</v>
+      </c>
+      <c r="D10" s="1">
         <v>0.5625</v>
       </c>
       <c r="E10">
@@ -583,7 +699,13 @@
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="D11">
+      <c r="B11" s="1">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="C11">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="D11" s="1">
         <v>0.59799999999999998</v>
       </c>
       <c r="E11">
@@ -594,14 +716,21 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="B12" s="1">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="C12">
+        <v>0.127</v>
+      </c>
+      <c r="D12" s="1">
         <v>0.94699999999999995</v>
       </c>
       <c r="E12">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Results.xlsx
+++ b/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658E56BC-F181-4AF6-A949-FA68FBB40E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583B9D7B-940A-4C36-9801-3E6D01B4BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Expon</t>
   </si>
@@ -83,7 +83,10 @@
     <t>Pima</t>
   </si>
   <si>
-    <t>PenDig</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>PenDigits</t>
   </si>
 </sst>
 </file>
@@ -138,7 +141,199 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -156,15 +351,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>124563</xdr:colOff>
+      <xdr:colOff>95988</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:colOff>409575</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -187,7 +382,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4001238" y="3162300"/>
+          <a:off x="3972663" y="3057525"/>
           <a:ext cx="4437912" cy="2105024"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -517,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF9C2C98-DB89-4AEF-8E03-799FADB9C11F}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -525,7 +720,7 @@
     <col min="8" max="8" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -542,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -558,8 +753,11 @@
       <c r="E2">
         <v>0.31269999999999998</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="1">
+        <v>0.69210000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -575,8 +773,11 @@
       <c r="E3">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>0.66993000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -592,8 +793,11 @@
       <c r="E4">
         <v>205.74</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1">
+        <v>0.84753999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -609,8 +813,11 @@
       <c r="E5">
         <v>2.27</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1">
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -626,8 +833,11 @@
       <c r="E6">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1">
+        <v>0.57347000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -643,8 +853,11 @@
       <c r="E7">
         <v>1.07</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="1">
+        <v>0.58291999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -660,8 +873,11 @@
       <c r="E8">
         <v>2.14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1">
+        <v>0.75566999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -677,8 +893,11 @@
       <c r="E9">
         <v>6.87</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1">
+        <v>0.90351999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -694,8 +913,11 @@
       <c r="E10">
         <v>1.44</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1">
+        <v>0.82892999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -711,10 +933,13 @@
       <c r="E11">
         <v>4.899</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1">
+        <v>0.76080999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1">
         <v>0.85799999999999998</v>
@@ -728,8 +953,26 @@
       <c r="E12">
         <v>0.106</v>
       </c>
+      <c r="F12" s="1">
+        <v>0.99212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B12">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>B2&gt;F2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D12">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>D2&gt;F2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583B9D7B-940A-4C36-9801-3E6D01B4BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6721C64-000E-49E4-BAF2-2FF6510A08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
   </bookViews>
@@ -141,7 +141,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -153,183 +153,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -350,23 +173,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>95988</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>857250</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>73428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C183262F-1EA1-0A4D-0542-A695BBF4279B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AB9FABE-B9BB-B8D2-747E-718C35BC3929}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -382,8 +205,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3972663" y="3057525"/>
-          <a:ext cx="4437912" cy="2105024"/>
+          <a:off x="3657600" y="3121428"/>
+          <a:ext cx="5086350" cy="2412596"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -748,10 +571,10 @@
         <v>0.49</v>
       </c>
       <c r="D2" s="1">
-        <v>0.92900000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="E2">
-        <v>0.31269999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="F2" s="1">
         <v>0.69210000000000005</v>
@@ -768,10 +591,10 @@
         <v>5.01</v>
       </c>
       <c r="D3" s="1">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>5.0999999999999996</v>
+        <v>10.53</v>
       </c>
       <c r="F3" s="1">
         <v>0.66993000000000003</v>
@@ -788,10 +611,10 @@
         <v>4094</v>
       </c>
       <c r="D4" s="1">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>205.74</v>
+        <v>24.62</v>
       </c>
       <c r="F4" s="1">
         <v>0.84753999999999996</v>
@@ -808,7 +631,7 @@
         <v>3.82</v>
       </c>
       <c r="D5" s="1">
-        <v>0.95699999999999996</v>
+        <v>0.91</v>
       </c>
       <c r="E5">
         <v>2.27</v>
@@ -831,7 +654,7 @@
         <v>0.51100000000000001</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1">
         <v>0.57347000000000004</v>
@@ -848,10 +671,10 @@
         <v>0.875</v>
       </c>
       <c r="D7" s="1">
-        <v>0.79700000000000004</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="E7">
-        <v>1.07</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="F7" s="1">
         <v>0.58291999999999999</v>
@@ -868,10 +691,10 @@
         <v>2.9</v>
       </c>
       <c r="D8" s="1">
-        <v>0.66400000000000003</v>
+        <v>0.69</v>
       </c>
       <c r="E8">
-        <v>2.14</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F8" s="1">
         <v>0.75566999999999995</v>
@@ -888,10 +711,10 @@
         <v>3.7</v>
       </c>
       <c r="D9" s="1">
-        <v>0.77</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="E9">
-        <v>6.87</v>
+        <v>3.43</v>
       </c>
       <c r="F9" s="1">
         <v>0.90351999999999999</v>
@@ -908,10 +731,10 @@
         <v>5.03</v>
       </c>
       <c r="D10" s="1">
-        <v>0.5625</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.44</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="F10" s="1">
         <v>0.82892999999999994</v>
@@ -928,7 +751,7 @@
         <v>9.4600000000000009</v>
       </c>
       <c r="D11" s="1">
-        <v>0.59799999999999998</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="E11">
         <v>4.899</v>
@@ -948,7 +771,7 @@
         <v>0.127</v>
       </c>
       <c r="D12" s="1">
-        <v>0.94699999999999995</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="E12">
         <v>0.106</v>
@@ -964,12 +787,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B12">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>B2&gt;F2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D12">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>D2&gt;F2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\Documents\GitHub\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6721C64-000E-49E4-BAF2-2FF6510A08BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75A5D57-6AE1-464C-9AD0-0E3883E9793E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Expon</t>
   </si>
@@ -54,12 +55,6 @@
   </si>
   <si>
     <t>Shuttle</t>
-  </si>
-  <si>
-    <t>Expon-Fit</t>
-  </si>
-  <si>
-    <t>Gamma-Fit</t>
   </si>
   <si>
     <t>WBC</t>
@@ -139,7 +134,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -167,55 +162,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>73428</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AB9FABE-B9BB-B8D2-747E-718C35BC3929}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3657600" y="3121428"/>
-          <a:ext cx="5086350" cy="2412596"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,268 +481,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF9C2C98-DB89-4AEF-8E03-799FADB9C11F}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>0.49</v>
+      <c r="C2" s="1">
+        <v>0.9</v>
       </c>
       <c r="D2" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="E2">
-        <v>0.35</v>
-      </c>
-      <c r="F2" s="1">
         <v>0.69210000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>5.01</v>
+      <c r="C3" s="1">
+        <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>10.53</v>
-      </c>
-      <c r="F3" s="1">
         <v>0.66993000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>0.98899999999999999</v>
       </c>
-      <c r="C4">
-        <v>4094</v>
+      <c r="C4" s="1">
+        <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>24.62</v>
-      </c>
-      <c r="F4" s="1">
         <v>0.84753999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>0.82350000000000001</v>
       </c>
-      <c r="C5">
-        <v>3.82</v>
+      <c r="C5" s="1">
+        <v>0.91</v>
       </c>
       <c r="D5" s="1">
-        <v>0.91</v>
-      </c>
-      <c r="E5">
-        <v>2.27</v>
-      </c>
-      <c r="F5" s="1">
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>0.55800000000000005</v>
       </c>
-      <c r="C6">
-        <v>12.6</v>
+      <c r="C6" s="1">
+        <v>0.51100000000000001</v>
       </c>
       <c r="D6" s="1">
-        <v>0.51100000000000001</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1">
         <v>0.57347000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>0.54800000000000004</v>
       </c>
-      <c r="C7">
-        <v>0.875</v>
+      <c r="C7" s="1">
+        <v>0.83299999999999996</v>
       </c>
       <c r="D7" s="1">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="E7">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="F7" s="1">
         <v>0.58291999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>2.9</v>
+      <c r="C8" s="1">
+        <v>0.69</v>
       </c>
       <c r="D8" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="E8">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="F8" s="1">
         <v>0.75566999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>0.88800000000000001</v>
       </c>
-      <c r="C9">
-        <v>3.7</v>
+      <c r="C9" s="1">
+        <v>0.84199999999999997</v>
       </c>
       <c r="D9" s="1">
-        <v>0.84199999999999997</v>
-      </c>
-      <c r="E9">
-        <v>3.43</v>
-      </c>
-      <c r="F9" s="1">
         <v>0.90351999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10">
-        <v>5.03</v>
+      <c r="C10" s="1">
+        <v>0.6</v>
       </c>
       <c r="D10" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="E10">
-        <v>0.93700000000000006</v>
-      </c>
-      <c r="F10" s="1">
         <v>0.82892999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
         <v>0.67100000000000004</v>
       </c>
-      <c r="C11">
-        <v>9.4600000000000009</v>
+      <c r="C11" s="1">
+        <v>0.58299999999999996</v>
       </c>
       <c r="D11" s="1">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="E11">
-        <v>4.899</v>
-      </c>
-      <c r="F11" s="1">
         <v>0.76080999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1">
         <v>0.85799999999999998</v>
       </c>
-      <c r="C12">
-        <v>0.127</v>
+      <c r="C12" s="1">
+        <v>0.95399999999999996</v>
       </c>
       <c r="D12" s="1">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="E12">
-        <v>0.106</v>
-      </c>
-      <c r="F12" s="1">
         <v>0.99212</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I13" t="s">
-        <v>15</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G13" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>B2&gt;F2</formula>
+      <formula>B2&gt;D2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>D2&gt;F2</formula>
+      <formula>C2&gt;D2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01FD6FE5-3D31-461D-9245-328CAA00BF7E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Results.xlsx
+++ b/Results.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\Documents\GitHub\Outlier-Detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75A5D57-6AE1-464C-9AD0-0E3883E9793E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0248A7-8771-4283-B08C-24B85C0E90FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{0683FA70-01DB-4579-95F0-754B7CFD4E13}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Expon</t>
   </si>
@@ -82,6 +81,18 @@
   </si>
   <si>
     <t>PenDigits</t>
+  </si>
+  <si>
+    <t>KNN</t>
+  </si>
+  <si>
+    <t>FastABOD</t>
+  </si>
+  <si>
+    <t>LDOF</t>
+  </si>
+  <si>
+    <t>LDF</t>
   </si>
 </sst>
 </file>
@@ -128,13 +139,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -482,13 +494,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF9C2C98-DB89-4AEF-8E03-799FADB9C11F}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1"/>
-    <col min="6" max="6" width="16.1328125" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -510,10 +523,13 @@
         <v>0.9</v>
       </c>
       <c r="D2" s="1">
-        <v>0.69210000000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+        <v>0.752</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -524,10 +540,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>0.66993000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+        <v>0.67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -540,8 +559,11 @@
       <c r="D4" s="1">
         <v>0.84753999999999996</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -554,8 +576,11 @@
       <c r="D5" s="1">
         <v>0.99717999999999996</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -568,8 +593,11 @@
       <c r="D6" s="1">
         <v>0.57347000000000004</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -582,8 +610,11 @@
       <c r="D7" s="1">
         <v>0.58291999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -596,8 +627,11 @@
       <c r="D8" s="1">
         <v>0.75566999999999995</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -610,8 +644,11 @@
       <c r="D9" s="1">
         <v>0.90351999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -624,8 +661,11 @@
       <c r="D10" s="1">
         <v>0.82892999999999994</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -638,8 +678,11 @@
       <c r="D11" s="1">
         <v>0.76080999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -652,8 +695,23 @@
       <c r="D12" s="1">
         <v>0.99212</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <f>AVERAGE(B2:B12)</f>
+        <v>0.8486818181818182</v>
+      </c>
+      <c r="C13" s="2">
+        <f>AVERAGE(C2:C12)</f>
+        <v>0.80209090909090897</v>
+      </c>
+      <c r="D13" s="2">
+        <f>AVERAGE(D2:D12)</f>
+        <v>0.78765090909090918</v>
+      </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
@@ -671,13 +729,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01FD6FE5-3D31-461D-9245-328CAA00BF7E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>